--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Pictures\curso_ds\testes\git\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6A739A-FC51-4B28-8E3C-3D2AF7E9C840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E95289-4E0E-4943-A134-54884266A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="533">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1596,6 +1596,63 @@
   </si>
   <si>
     <t>Colocar nome completo separado por espacos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selecao de filmes,  Selecao de acentos, adicinar item na bomboniere, escolher forma de pagamento , Dados pessoais </t>
+  </si>
+  <si>
+    <t>Verificar se as funçoes estao de acordo com as regras de negocio</t>
+  </si>
+  <si>
+    <t>Unitario, sistema , aceitação</t>
+  </si>
+  <si>
+    <t>Devtools, vscode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A partir do momento que os arquivos e  o teste de fumaca for executado </t>
+  </si>
+  <si>
+    <t>Pelo menos 90% dos casos  de teste executados tiveram passado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insercao de valores alem do limite, selecionar mais de um campo , colocar valor invalidos, numero negativos </t>
+  </si>
+  <si>
+    <t>tudo relacionado ao visual do sistemas ou backend e banco de dados</t>
+  </si>
+  <si>
+    <t>Funcionalidades repondendo de acordo com as regra de negocio</t>
+  </si>
+  <si>
+    <t>CA01.1</t>
+  </si>
+  <si>
+    <t>verificar se todas as funciononalidade do sistema estão de acordo com os requisitos de negocio</t>
+  </si>
+  <si>
+    <t>CA01.2</t>
+  </si>
+  <si>
+    <t>Preco por Horario</t>
+  </si>
+  <si>
+    <t>Acento não selecionado</t>
+  </si>
+  <si>
+    <t>1.Selecionar horario, 2.Selecionar Acento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor do ingresso R$32,00 </t>
+  </si>
+  <si>
+    <t>Preco por Horario antes das cinco</t>
+  </si>
+  <si>
+    <t>1. Selecionar horario antes das cinco                 2. Selecionar Acento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor do ingresso R$24,00 </t>
   </si>
 </sst>
 </file>
@@ -1748,11 +1805,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1801,6 +1855,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2073,206 +2131,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2298,330 +2356,330 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2680,100 +2738,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2816,263 +2874,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="B4" s="17"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="9" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="9" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="10" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="9" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3120,147 +3178,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3289,382 +3347,382 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="6" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="6" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="6" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>494</v>
       </c>
     </row>
@@ -3684,92 +3742,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="20">
         <v>46323</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="21">
         <v>0.80208333333333337</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3791,146 +3849,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="23" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="D16" s="25"/>
+      <c r="D16" s="24"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="25"/>
+      <c r="B20" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3975,198 +4033,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="23" t="s">
         <v>502</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="23" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="23" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="23" t="s">
         <v>508</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="23" t="s">
         <v>509</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="23" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="H14" s="25"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E18" s="25"/>
+      <c r="E18" s="24"/>
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="F19" s="25"/>
@@ -4212,208 +4270,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="23" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="23" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="23" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C30" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -4463,864 +4567,892 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B6" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>531</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5400,678 +5532,678 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6157,300 +6289,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6509,356 +6641,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Pictures\curso_ds\testes\git\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E95289-4E0E-4943-A134-54884266A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F8592E-632E-4C44-A854-2013A6EAE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="552">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1562,42 +1562,9 @@
     <t>Todos elemento de ui funcionando corretamente.</t>
   </si>
   <si>
-    <t>Cupom Pipoca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o requisito diz que um ingresso + pipoca grande o desconto é de R$ 3,20 </t>
-  </si>
-  <si>
-    <t>Alguma messagem que explique que o desconto é somente para o valor do ingresso</t>
-  </si>
-  <si>
-    <t>Desconto Pix</t>
-  </si>
-  <si>
-    <t>Alterna entre o pagamento pix e cartão acumula desconto do pix</t>
-  </si>
-  <si>
-    <t>O desconto do pix não pode ser acumulativo</t>
-  </si>
-  <si>
-    <t>Parcelamento do Cartao</t>
-  </si>
-  <si>
-    <t>limiites de centavos não permite o parcelamento para 6x</t>
-  </si>
-  <si>
-    <t>porque não colocar o valor minimo baseado no consumo medio?</t>
-  </si>
-  <si>
     <t>Nome Completo</t>
   </si>
   <si>
-    <t xml:space="preserve">Não exite nome com no minido 3 caracteres </t>
-  </si>
-  <si>
-    <t>Colocar nome completo separado por espacos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Selecao de filmes,  Selecao de acentos, adicinar item na bomboniere, escolher forma de pagamento , Dados pessoais </t>
   </si>
   <si>
@@ -1631,35 +1598,125 @@
     <t>verificar se todas as funciononalidade do sistema estão de acordo com os requisitos de negocio</t>
   </si>
   <si>
-    <t>CA01.2</t>
-  </si>
-  <si>
-    <t>Preco por Horario</t>
-  </si>
-  <si>
-    <t>Acento não selecionado</t>
-  </si>
-  <si>
-    <t>1.Selecionar horario, 2.Selecionar Acento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor do ingresso R$32,00 </t>
-  </si>
-  <si>
-    <t>Preco por Horario antes das cinco</t>
-  </si>
-  <si>
-    <t>1. Selecionar horario antes das cinco                 2. Selecionar Acento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor do ingresso R$24,00 </t>
+    <t xml:space="preserve">Desconto pix </t>
+  </si>
+  <si>
+    <t>O requisito define um limite que não faz sentido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definir um novo limite baseado na soma dos vendidos </t>
+  </si>
+  <si>
+    <t>a quantidade de caracteres para um nome e muito pequena baseado no padrao de nome brasileiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exite algum nome com 3 caracteres?. </t>
+  </si>
+  <si>
+    <t>Com as correções verificar se o sistema esta funcinando corretamente</t>
+  </si>
+  <si>
+    <t>Tenta identificar erros que não tenha no plano de teste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simular se sistema aguenta uma quantidade de usuario e uma pre-estreia </t>
+  </si>
+  <si>
+    <t>Para discobri quando sistema trava para tomar medidas.</t>
+  </si>
+  <si>
+    <t>Analisar quanto tempo um usuario leva pra compra um ingresso e se atividade e facil de ser exeutada</t>
+  </si>
+  <si>
+    <t>Verificar se o sistema esta de acordo com os requisitos</t>
+  </si>
+  <si>
+    <t>CA02.1</t>
+  </si>
+  <si>
+    <t>CA03.1</t>
+  </si>
+  <si>
+    <t>CA04.1</t>
+  </si>
+  <si>
+    <t>CA05.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preco da seção </t>
+  </si>
+  <si>
+    <t>acento selecionado</t>
+  </si>
+  <si>
+    <t>O valor do ingresso e exibido R$24,00</t>
+  </si>
+  <si>
+    <t>Valor da sala 3D</t>
+  </si>
+  <si>
+    <t>Horario e Acento selecionado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Selecionar Horario                                         2.Selecionar Acento                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Selecionar horario com filme 3D depois das 17                                                                 2. Selecionar acento </t>
+  </si>
+  <si>
+    <t>O valor da seção tem que ser R$38,00</t>
+  </si>
+  <si>
+    <t>Aplicação de Meia entrada</t>
+  </si>
+  <si>
+    <t>1.Selecionar Horario depois da 17                      2.Selecionar acento                                          3.adicionar uma meia entrada</t>
+  </si>
+  <si>
+    <t>Digita 1 na  meia entrada</t>
+  </si>
+  <si>
+    <t>No resumo exibir o valor do ingresso com metade do preco</t>
+  </si>
+  <si>
+    <t>Pre-estreia sem meia  entrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Selecionar horario com pre-estreia                  2.selecionar acento                                           3.adicionar meia entrada </t>
+  </si>
+  <si>
+    <t>O valor do ingresso com a meia-entradada não aplicado</t>
+  </si>
+  <si>
+    <t>Não confirmar pedido sem ingresso</t>
+  </si>
+  <si>
+    <t>Selecionar horario</t>
+  </si>
+  <si>
+    <t>1.selecionar horario                                          2.confirmar pedido</t>
+  </si>
+  <si>
+    <t>Mensagem dizendo que precisa selecionar um acento para confirmar</t>
+  </si>
+  <si>
+    <t>CA05.2</t>
+  </si>
+  <si>
+    <t>Limite de acentos</t>
+  </si>
+  <si>
+    <t>1.selecionar horario                                           2.selecionar mais de 6 acentos</t>
+  </si>
+  <si>
+    <t>No resumo exibir o valor total do ingresso de acordo com 6  acentos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1731,6 +1788,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1805,7 +1870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1858,6 +1923,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2895,7 +2963,7 @@
       </c>
       <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -4082,24 +4150,24 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -4107,60 +4175,40 @@
         <v>100</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>484</v>
+        <v>94</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>460</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>509</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>510</v>
-      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>511</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>512</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>513</v>
-      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -4231,7 +4279,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -4261,7 +4309,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4284,7 +4332,7 @@
         <v>111</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4292,7 +4340,7 @@
         <v>112</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>113</v>
@@ -4303,7 +4351,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4322,7 +4370,7 @@
         <v>117</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4330,7 +4378,7 @@
         <v>118</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>119</v>
@@ -4341,7 +4389,7 @@
         <v>120</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>121</v>
@@ -4352,7 +4400,7 @@
         <v>122</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>123</v>
@@ -4363,7 +4411,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>125</v>
@@ -4374,7 +4422,7 @@
         <v>126</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>127</v>
@@ -4413,7 +4461,7 @@
         <v>435</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -4423,7 +4471,9 @@
       <c r="B20" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C20" s="8"/>
+      <c r="C20" s="23" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
@@ -4441,7 +4491,9 @@
       <c r="B22" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C22" s="8"/>
+      <c r="C22" s="23" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
@@ -4452,14 +4504,16 @@
       </c>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>139</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C24" s="8"/>
+      <c r="C24" s="23" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
@@ -4468,7 +4522,9 @@
       <c r="B25" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="23" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
@@ -4497,14 +4553,16 @@
       </c>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>144</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="23" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
@@ -4513,7 +4571,12 @@
       <c r="B30" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="8"/>
+      <c r="C30" s="23" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4601,7 +4664,7 @@
       <c r="H4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="27" t="s">
         <v>153</v>
       </c>
       <c r="J4" s="10" t="s">
@@ -4666,7 +4729,7 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>171</v>
       </c>
@@ -4674,135 +4737,219 @@
         <v>433</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D6" s="8"/>
+        <v>512</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>463</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="G6" s="23" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="23" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>172</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>523</v>
-      </c>
-      <c r="D7" s="8"/>
+        <v>525</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>463</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="G7" s="23" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="23" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>540</v>
+      </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="B9" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>543</v>
+      </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>546</v>
+      </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="23" t="s">
+        <v>547</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>549</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>550</v>
+      </c>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="23" t="s">
+        <v>551</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
@@ -4840,7 +4987,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Pictures\curso_ds\testes\git\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F8592E-632E-4C44-A854-2013A6EAE24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF1C50E-35CA-433D-92D0-57AF92B2D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="564">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1710,6 +1710,42 @@
   </si>
   <si>
     <t>No resumo exibir o valor total do ingresso de acordo com 6  acentos</t>
+  </si>
+  <si>
+    <t>CA05.3</t>
+  </si>
+  <si>
+    <t>Limite de acentos utrapassados</t>
+  </si>
+  <si>
+    <t>1.Selecionar horario                                          2.selecionar mais de 6 acentos</t>
+  </si>
+  <si>
+    <t>Aviso do sistema que o limite foi utrapassado</t>
+  </si>
+  <si>
+    <t>CA07.1</t>
+  </si>
+  <si>
+    <t>Limite na bomboniere</t>
+  </si>
+  <si>
+    <t>Selecionar horario e acento</t>
+  </si>
+  <si>
+    <t>1.selecionar horario                                          2.selecionar acento                                           3.colocar na bomboniere valor acima de 10</t>
+  </si>
+  <si>
+    <t>Valor e resetado para 10</t>
+  </si>
+  <si>
+    <t>CA07.2</t>
+  </si>
+  <si>
+    <t>Numeros negativos</t>
+  </si>
+  <si>
+    <t>1. Selecionar horario                                         2. Selecionar acento                                         3. colocar valor negativo na bomboniere</t>
   </si>
 </sst>
 </file>
@@ -1921,11 +1957,11 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2963,7 +2999,7 @@
       </c>
       <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3017,7 +3053,7 @@
       </c>
       <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -3139,8 +3175,8 @@
       <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
       <c r="D26" s="9" t="s">
         <v>395</v>
       </c>
@@ -3149,29 +3185,29 @@
       <c r="A27" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
       <c r="D30" s="9" t="s">
         <v>400</v>
       </c>
@@ -3180,8 +3216,8 @@
       <c r="A31" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="9" t="s">
         <v>402</v>
       </c>
@@ -3190,15 +3226,15 @@
       <c r="A32" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4664,7 +4700,7 @@
       <c r="H4" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="26" t="s">
         <v>153</v>
       </c>
       <c r="J4" s="10" t="s">
@@ -4955,59 +4991,107 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>553</v>
+      </c>
       <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="I12" s="8" t="s">
+        <v>554</v>
+      </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>555</v>
+      </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>559</v>
+      </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="22"/>
+      <c r="K13" s="22" t="s">
+        <v>560</v>
+      </c>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>562</v>
+      </c>
       <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="I14" s="23" t="s">
+        <v>563</v>
+      </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="22"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
@@ -5603,7 +5687,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Pictures\curso_ds\testes\git\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF1C50E-35CA-433D-92D0-57AF92B2D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677E5D5E-C84E-4A1F-B919-AC659DBB0DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="642">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -1631,128 +1631,362 @@
     <t>Verificar se o sistema esta de acordo com os requisitos</t>
   </si>
   <si>
-    <t>CA02.1</t>
-  </si>
-  <si>
-    <t>CA03.1</t>
-  </si>
-  <si>
     <t>CA04.1</t>
   </si>
   <si>
-    <t>CA05.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preco da seção </t>
-  </si>
-  <si>
-    <t>acento selecionado</t>
-  </si>
-  <si>
-    <t>O valor do ingresso e exibido R$24,00</t>
-  </si>
-  <si>
-    <t>Valor da sala 3D</t>
-  </si>
-  <si>
-    <t>Horario e Acento selecionado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Selecionar Horario                                         2.Selecionar Acento                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Selecionar horario com filme 3D depois das 17                                                                 2. Selecionar acento </t>
-  </si>
-  <si>
-    <t>O valor da seção tem que ser R$38,00</t>
-  </si>
-  <si>
-    <t>Aplicação de Meia entrada</t>
-  </si>
-  <si>
-    <t>1.Selecionar Horario depois da 17                      2.Selecionar acento                                          3.adicionar uma meia entrada</t>
-  </si>
-  <si>
-    <t>Digita 1 na  meia entrada</t>
-  </si>
-  <si>
-    <t>No resumo exibir o valor do ingresso com metade do preco</t>
-  </si>
-  <si>
-    <t>Pre-estreia sem meia  entrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Selecionar horario com pre-estreia                  2.selecionar acento                                           3.adicionar meia entrada </t>
-  </si>
-  <si>
-    <t>O valor do ingresso com a meia-entradada não aplicado</t>
-  </si>
-  <si>
-    <t>Não confirmar pedido sem ingresso</t>
-  </si>
-  <si>
-    <t>Selecionar horario</t>
-  </si>
-  <si>
-    <t>1.selecionar horario                                          2.confirmar pedido</t>
-  </si>
-  <si>
-    <t>Mensagem dizendo que precisa selecionar um acento para confirmar</t>
-  </si>
-  <si>
-    <t>CA05.2</t>
-  </si>
-  <si>
-    <t>Limite de acentos</t>
-  </si>
-  <si>
-    <t>1.selecionar horario                                           2.selecionar mais de 6 acentos</t>
-  </si>
-  <si>
-    <t>No resumo exibir o valor total do ingresso de acordo com 6  acentos</t>
-  </si>
-  <si>
     <t>CA05.3</t>
   </si>
   <si>
-    <t>Limite de acentos utrapassados</t>
-  </si>
-  <si>
-    <t>1.Selecionar horario                                          2.selecionar mais de 6 acentos</t>
-  </si>
-  <si>
-    <t>Aviso do sistema que o limite foi utrapassado</t>
-  </si>
-  <si>
     <t>CA07.1</t>
   </si>
   <si>
-    <t>Limite na bomboniere</t>
-  </si>
-  <si>
-    <t>Selecionar horario e acento</t>
-  </si>
-  <si>
-    <t>1.selecionar horario                                          2.selecionar acento                                           3.colocar na bomboniere valor acima de 10</t>
-  </si>
-  <si>
-    <t>Valor e resetado para 10</t>
-  </si>
-  <si>
-    <t>CA07.2</t>
-  </si>
-  <si>
-    <t>Numeros negativos</t>
-  </si>
-  <si>
-    <t>1. Selecionar horario                                         2. Selecionar acento                                         3. colocar valor negativo na bomboniere</t>
+    <t>Validar preço de inteira para sessão em horário de matinê</t>
+  </si>
+  <si>
+    <t>O sistema está aberto na página principal e há sessão do filme 'Órbita Silenciosa' às 14:00.</t>
+  </si>
+  <si>
+    <t>1. Selecionar o filme 'Órbita Silenciosa'. 2. Escolher a sessão das 14:00 (2D). 3. Selecionar 1 assento. 4. Observar o valor do ingresso inteiro no resumo.</t>
+  </si>
+  <si>
+    <t>Filme: Órbita Silenciosa, Sessão: 14:00 (2D), Quantidade: 1 inteira.</t>
+  </si>
+  <si>
+    <t>O valor unitário do ingresso inteiro deve ser exibido como R$ 24,00.</t>
+  </si>
+  <si>
+    <t>CA01.3</t>
+  </si>
+  <si>
+    <t>Validar preço de inteira para sessão iniciada após as 17:00</t>
+  </si>
+  <si>
+    <t>O sistema está aberto na página principal.</t>
+  </si>
+  <si>
+    <t>1. Selecionar o filme 'O Último Farol'. 2. Escolher a sessão das 21:00 (2D). 3. Selecionar 1 assento. 4. Verificar o subtotal de ingressos.</t>
+  </si>
+  <si>
+    <t>Filme: O Último Farol, Sessão: 21:00 (2D), Quantidade: 1 inteira.</t>
+  </si>
+  <si>
+    <t>O valor unitário do ingresso inteiro deve ser de R$ 32,00.</t>
+  </si>
+  <si>
+    <t>CA02.2</t>
+  </si>
+  <si>
+    <t>Validar aplicação do adicional 3D para múltiplos ingressos</t>
+  </si>
+  <si>
+    <t>1. Selecionar o filme 'Órbita Silenciosa'. 2. Escolher a sessão das 20:30 (3D). 3. Selecionar 2 assentos. 4. Verificar o subtotal dos ingressos.</t>
+  </si>
+  <si>
+    <t>Filme: Órbita Silenciosa, Sessão: 20:30 (3D), Ingressos: 2 inteiras.</t>
+  </si>
+  <si>
+    <t>Cada ingresso deve custar R$ 32,00 + R$ 6,00 (totalizando R$ 38,00 cada), resultando em um subtotal de R$ 76,00.</t>
+  </si>
+  <si>
+    <t>CA03.2</t>
+  </si>
+  <si>
+    <t>Validar cálculo de meia-entrada em sessão 3D</t>
+  </si>
+  <si>
+    <t>1. Selecionar o filme 'Órbita Silenciosa'. 2. Escolher a sessão das 20:30 (3D). 3. Selecionar 1 assento. 4. Marcar o ingresso como meia-entrada. 5. Verificar o valor cobrado pelo ingresso.</t>
+  </si>
+  <si>
+    <t>Sessão: 20:30 (3D), Tipo de ingresso: 1 meia-entrada.</t>
+  </si>
+  <si>
+    <t>O valor da meia-entrada deve ser 50% do valor total do ingresso (R$ 38,00), resultando em R$ 19,00.</t>
+  </si>
+  <si>
+    <t>Verificar restrição de meia-entrada em sessão de pré-estreia</t>
+  </si>
+  <si>
+    <t>1. Selecionar o filme 'Cidade de Vidro' (Pré-estreia). 2. Escolher a sessão das 22:00 (2D). 3. Selecionar 1 assento. 4. Tentar marcar como meia-entrada. 5. Verificar o preço cobrado.</t>
+  </si>
+  <si>
+    <t>Sessão de pré-estreia, tentativa de seleção de meia-entrada.</t>
+  </si>
+  <si>
+    <t>A opção de meia-entrada não deve alterar o preço, cobrando o valor integral de R$ 32,00.</t>
+  </si>
+  <si>
+    <t>Validar limite máximo de 6 ingressos por pedido</t>
+  </si>
+  <si>
+    <t>O usuário selecionou uma sessão válida e já marcou 6 assentos no mapa da sala.</t>
+  </si>
+  <si>
+    <t>1. Clicar em um 7º assento livre no mapa da sala. 2. Observar o comportamento da interface.</t>
+  </si>
+  <si>
+    <t>Tentativa de seleção do 7º assento.</t>
+  </si>
+  <si>
+    <t>O sistema deve recusar a seleção do 7º assento e exibir um aviso ao cliente.</t>
+  </si>
+  <si>
+    <t>CA06.2</t>
+  </si>
+  <si>
+    <t>Desfazer seleção de assento ao clicar novamente</t>
+  </si>
+  <si>
+    <t>O usuário escolheu uma sessão e marcou 1 assento.</t>
+  </si>
+  <si>
+    <t>1. Clicar novamente sobre o assento já selecionado. 2. Verificar o status do assento e o valor do pedido.</t>
+  </si>
+  <si>
+    <t>Clique duplo no mesmo assento selecionado.</t>
+  </si>
+  <si>
+    <t>O assento deve ser liberado (desmarcado), retirado do mapa de seleção e o valor dos ingressos deve voltar a zero.</t>
+  </si>
+  <si>
+    <t>Validar quantidade máxima de itens na bomboniere</t>
+  </si>
+  <si>
+    <t>O usuário está na etapa de seleção da bomboniere.</t>
+  </si>
+  <si>
+    <t>1. Digitar o valor 12 no campo de quantidade da 'Pipoca pequena'. 2. Sair do campo (perder o foco). 3. Verificar o valor assumido pelo campo.</t>
+  </si>
+  <si>
+    <t>Quantidade informada: 12.</t>
+  </si>
+  <si>
+    <t>O sistema deve corrigir automaticamente o valor para o limite máximo permitido, que é 10.</t>
+  </si>
+  <si>
+    <t>CA08.2</t>
+  </si>
+  <si>
+    <t>Validar incidência da taxa de conveniência apenas sobre ingressos</t>
+  </si>
+  <si>
+    <t>O usuário adicionou 1 ingresso e 2 unidades de pipoca pequena ao pedido.</t>
+  </si>
+  <si>
+    <t>1. Visualizar o detalhamento do resumo de valores. 2. Calcular a taxa de conveniência aplicada.</t>
+  </si>
+  <si>
+    <t>1 Ingresso e 2 Pipocas pequenas.</t>
+  </si>
+  <si>
+    <t>A taxa de conveniência deve ser cobrada apenas com base na quantidade de ingressos (1 ingresso = R$ 2,50), sem incidir sobre os itens da bomboniere.</t>
+  </si>
+  <si>
+    <t>CA09.2</t>
+  </si>
+  <si>
+    <t>Tabela de Decisão</t>
+  </si>
+  <si>
+    <t>Validar flexibilidade de formatação no cupom CINE10</t>
+  </si>
+  <si>
+    <t>O usuário possui itens de ingresso no carrinho.</t>
+  </si>
+  <si>
+    <t>1. Digitar o cupom com espaços e letras minúsculas (` cIne10 `) no campo de cupons. 2. Aplicar o cupom. 3. Verificar se o desconto foi concedido.</t>
+  </si>
+  <si>
+    <t>String de cupom: ` cIne10 `</t>
+  </si>
+  <si>
+    <t>O cupom deve ser aceito independentemente de letras maiúsculas/minúsculas e espaços nas pontas, aplicando 10% de desconto sobre o subtotal de ingressos.</t>
+  </si>
+  <si>
+    <t>CA10.2</t>
+  </si>
+  <si>
+    <t>Validar rejeição do cupom PIPOCA5 abaixo do valor mínimo</t>
+  </si>
+  <si>
+    <t>O usuário possui itens de bomboniere com subtotal inferior a R$ 25,00 no carrinho (ex: 1 Refrigerante de R$ 9,50).</t>
+  </si>
+  <si>
+    <t>1. Inserir o cupom `PIPOCA5`. 2. Tentar aplicar. 3. Verificar a mensagem exibida.</t>
+  </si>
+  <si>
+    <t>Cupom: `PIPOCA5`, Subtotal da bomboniere: R$ 9,50.</t>
+  </si>
+  <si>
+    <t>O cupom deve ser recusado e uma mensagem explicativa de restrição deve ser exibida.</t>
+  </si>
+  <si>
+    <t>CA11.2</t>
+  </si>
+  <si>
+    <t>Validar remoção do desconto Pix ao alterar forma de pagamento</t>
+  </si>
+  <si>
+    <t>O usuário selecionou a forma de pagamento Pix e o desconto de 5% foi aplicado ao total.</t>
+  </si>
+  <si>
+    <t>1. Alterar a forma de pagamento de Pix para Cartão de Crédito. 2. Verificar o valor total do pedido.</t>
+  </si>
+  <si>
+    <t>Troca de Pix para Cartão.</t>
+  </si>
+  <si>
+    <t>O desconto de 5% associado ao Pix deve ser removido imediatamente do valor total.</t>
+  </si>
+  <si>
+    <t>CA12.1</t>
+  </si>
+  <si>
+    <t>Validar limite de parcelamento para pedidos abaixo de R$ 150,00</t>
+  </si>
+  <si>
+    <t>O usuário selecionou Cartão de Crédito como forma de pagamento e o valor total do pedido é de R$ 149,99.</t>
+  </si>
+  <si>
+    <t>1. Abrir o seletor de parcelas do cartão de crédito. 2. Verificar o número máximo de parcelas disponíveis.</t>
+  </si>
+  <si>
+    <t>Valor total do pedido: R$ 149,99.</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir o parcelamento em no máximo 3x sem juros.</t>
+  </si>
+  <si>
+    <t>CA13.1</t>
+  </si>
+  <si>
+    <t>Validar validação de tamanho mínimo para o campo Nome Completo</t>
+  </si>
+  <si>
+    <t>O usuário chegou na etapa de preenchimento dos dados do comprador.</t>
+  </si>
+  <si>
+    <t>1. Digitar um nome com 2 caracteres ('An'). 2. Tentar prosseguir/confirmar a compra. 3. Limpar e digitar um nome com 3 caracteres ('Ana'). 4. Tentar prosseguir.</t>
+  </si>
+  <si>
+    <t>'An' (inválido) e 'Ana' (válido).</t>
+  </si>
+  <si>
+    <t>O nome com 2 caracteres deve ser recusado com mensagem de erro; o nome com 3 caracteres deve ser aceito.</t>
+  </si>
+  <si>
+    <t>Validar validação do formato do e-mail do comprador</t>
+  </si>
+  <si>
+    <t>O usuário está preenchendo os dados do comprador.</t>
+  </si>
+  <si>
+    <t>1. Informar um e-mail sem o caractere arroba (`clientecinema.com`). 2. Tentar confirmar a compra.</t>
+  </si>
+  <si>
+    <t>E-mail inválido: `clientecinema.com`</t>
+  </si>
+  <si>
+    <t>O sistema deve recusar o formato do e-mail, impedir a confirmação e exibir mensagem de erro correspondente.</t>
+  </si>
+  <si>
+    <t>CA16.1</t>
+  </si>
+  <si>
+    <t>Verificar persistência do pedido em andamento após recarregar a página (F5)</t>
+  </si>
+  <si>
+    <t>O usuário selecionou a sessão, assentos e alguns itens de bomboniere.</t>
+  </si>
+  <si>
+    <t>1. Pressionar a tecla `F5` para recarregar a página do navegador antes de confirmar a compra. 2. Verificar se os dados selecionados foram mantidos.</t>
+  </si>
+  <si>
+    <t>Ação de recarregar a página (F5).</t>
+  </si>
+  <si>
+    <t>A sessão, os assentos escolhidos e os itens da bomboniere devem continuar selecionados na interface após o refresh.</t>
+  </si>
+  <si>
+    <t>CA18.1</t>
+  </si>
+  <si>
+    <t>Validar proteção contra execução de tags HTML nos dados do comprador</t>
+  </si>
+  <si>
+    <t>O usuário está na tela de preenchimento dos dados do comprador.</t>
+  </si>
+  <si>
+    <t>1. Inserir tag HTML no campo de Nome Completo (`&lt;b&gt;Ana&lt;/b&gt;`). 2. Concluir a compra e verificar a tela de confirmação.</t>
+  </si>
+  <si>
+    <t>Nome: `&lt;b&gt;Ana&lt;/b&gt;`</t>
+  </si>
+  <si>
+    <t>O conteúdo deve ser exibido estritamente como texto literal (sem aplicação de formatação de negrito ou execução de script).</t>
+  </si>
+  <si>
+    <t>CA19.1</t>
+  </si>
+  <si>
+    <t>Validar navegação e fluxo de compra completo utilizando apenas o teclado</t>
+  </si>
+  <si>
+    <t>O sistema está aberto na página inicial, sem o uso do mouse.</t>
+  </si>
+  <si>
+    <t>1. Utilizar as teclas `Tab`, `Shift+Tab`, setas direcionais, `Enter` e `Espaço`. 2. Selecionar filme, sessão, assentos, preencher dados e confirmar a compra.</t>
+  </si>
+  <si>
+    <t>Comandos exclusivos via teclado.</t>
+  </si>
+  <si>
+    <t>Toda a jornada de compra deve ser concluída com sucesso sem a necessidade de interagir com o mouse.</t>
+  </si>
+  <si>
+    <t>CA20.1</t>
+  </si>
+  <si>
+    <t>Validar formatação padrão brasileira de moeda em todos os campos de valores</t>
+  </si>
+  <si>
+    <t>O usuário adicionou ingressos e itens ao carrinho.</t>
+  </si>
+  <si>
+    <t>1. Inspecionar todas as linhas de resumo de preços (ingressos, taxa, bomboniere, descontos e total).</t>
+  </si>
+  <si>
+    <t>Valores calculados no carrinho.</t>
+  </si>
+  <si>
+    <t>Todos os valores monetários devem seguir rigorosamente o padrão brasileiro com o prefixo 'R$', vírgula como separador decimal e duas casas decimais (ex: R$ 23,70).</t>
+  </si>
+  <si>
+    <t>CA21.1</t>
+  </si>
+  <si>
+    <t>Caixa Branca</t>
+  </si>
+  <si>
+    <t>Validar integridade dos preços contra manipulação via DevTools</t>
+  </si>
+  <si>
+    <t>O usuário está na etapa final de pagamento com produtos no carrinho.</t>
+  </si>
+  <si>
+    <t>1. Abrir as Ferramentas de Desenvolvedor (DevTools) do navegador. 2. Alterar o atributo de preço de um ingresso ou o valor total exibido no DOM. 3. Clicar em 'Confirmar compra' e verificar o valor registrado.</t>
+  </si>
+  <si>
+    <t>Manipulação manual de elementos HTML/atributos de preço via DevTools.</t>
+  </si>
+  <si>
+    <t>A alteração feita no cliente via DevTools não deve impactar o valor cobrado/processado pelo sistema de regras de negócio (backend simulado).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1833,6 +2067,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1906,7 +2146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1961,6 +2201,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2999,7 +3242,7 @@
       </c>
       <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3053,7 +3296,7 @@
       </c>
       <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -4765,7 +5008,7 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>171</v>
       </c>
@@ -4776,185 +5019,191 @@
         <v>512</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>463</v>
+        <v>162</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G6" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>529</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="I6" s="23" t="s">
         <v>530</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>534</v>
-      </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>531</v>
+      </c>
       <c r="K6" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>172</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="J7" s="8"/>
+        <v>536</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>537</v>
+      </c>
       <c r="K7" s="23" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>173</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>463</v>
+        <v>162</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>175</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>546</v>
-      </c>
-      <c r="J10" s="8"/>
+        <v>550</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>551</v>
+      </c>
       <c r="K10" s="23" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>176</v>
       </c>
@@ -4962,71 +5211,77 @@
         <v>469</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>137</v>
+        <v>444</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>550</v>
-      </c>
-      <c r="J11" s="8"/>
+        <v>555</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>556</v>
+      </c>
       <c r="K11" s="23" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>134</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>445</v>
+        <v>163</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="H12" s="8"/>
+        <v>559</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>560</v>
+      </c>
       <c r="I12" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="J12" s="8"/>
+        <v>561</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>562</v>
+      </c>
       <c r="K12" s="8" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>178</v>
       </c>
@@ -5034,7 +5289,7 @@
         <v>476</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>444</v>
@@ -5043,35 +5298,37 @@
         <v>134</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>434</v>
+        <v>163</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="J13" s="8"/>
+        <v>566</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>567</v>
+      </c>
       <c r="K13" s="22" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>179</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>162</v>
@@ -5080,226 +5337,452 @@
         <v>134</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>434</v>
+        <v>163</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>562</v>
-      </c>
-      <c r="H14" s="8"/>
+        <v>570</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>571</v>
+      </c>
       <c r="I14" s="23" t="s">
-        <v>563</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+        <v>572</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>574</v>
+      </c>
       <c r="L14" s="22"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>581</v>
+      </c>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>587</v>
+      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:15" s="25" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>589</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>590</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>591</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>592</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+    </row>
+    <row r="18" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>605</v>
+      </c>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>610</v>
+      </c>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
+      <c r="B21" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>616</v>
+      </c>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>622</v>
+      </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>628</v>
+      </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>634</v>
+      </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>641</v>
+      </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>

--- a/relatorio/Relatorio_de_Testes_CineLume.xlsx
+++ b/relatorio/Relatorio_de_Testes_CineLume.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Pictures\curso_ds\testes\git\cinelume-qa\relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677E5D5E-C84E-4A1F-B919-AC659DBB0DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87922671-335A-4963-B882-5CAB414FEA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_Instrucoes" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,12 @@
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="776">
   <si>
     <t>Relatório de Testes — CineLume v1.0</t>
   </si>
@@ -761,9 +758,6 @@
     <t>BUG-04</t>
   </si>
   <si>
-    <t>BUG-05</t>
-  </si>
-  <si>
     <t>BUG-06</t>
   </si>
   <si>
@@ -1961,38 +1955,463 @@
     <t>Todos os valores monetários devem seguir rigorosamente o padrão brasileiro com o prefixo 'R$', vírgula como separador decimal e duas casas decimais (ex: R$ 23,70).</t>
   </si>
   <si>
-    <t>CA21.1</t>
-  </si>
-  <si>
-    <t>Caixa Branca</t>
-  </si>
-  <si>
-    <t>Validar integridade dos preços contra manipulação via DevTools</t>
-  </si>
-  <si>
-    <t>O usuário está na etapa final de pagamento com produtos no carrinho.</t>
-  </si>
-  <si>
-    <t>1. Abrir as Ferramentas de Desenvolvedor (DevTools) do navegador. 2. Alterar o atributo de preço de um ingresso ou o valor total exibido no DOM. 3. Clicar em 'Confirmar compra' e verificar o valor registrado.</t>
-  </si>
-  <si>
-    <t>Manipulação manual de elementos HTML/atributos de preço via DevTools.</t>
-  </si>
-  <si>
-    <t>A alteração feita no cliente via DevTools não deve impactar o valor cobrado/processado pelo sistema de regras de negócio (backend simulado).</t>
+    <t>Erro ao carregar lista de filmes na etapa 1</t>
+  </si>
+  <si>
+    <t>RN-01: O sistema deve carregar a lista de filmes disponíveis via dados.js ao iniciar.</t>
+  </si>
+  <si>
+    <t>CA-01: A seção de filmes deve exibir os pôsteres e horários corretamente.</t>
+  </si>
+  <si>
+    <t>CT-01: Validar carregamento inicial da lista de filmes</t>
+  </si>
+  <si>
+    <t>Critica</t>
+  </si>
+  <si>
+    <t>Nenhum (carregamento automático)</t>
+  </si>
+  <si>
+    <t>Os filmes disponíveis devem aparecer listados com suas respectivas sessões.</t>
+  </si>
+  <si>
+    <t>Mapa de assentos não exibe status atualizado após escolha da sessão</t>
+  </si>
+  <si>
+    <t>RN-02: O mapa de assentos deve refletir o estado de ocupação (livre, ocupado) da sessão selecionada.</t>
+  </si>
+  <si>
+    <t>CA-02: Assentos ocupados não devem permitir seleção.</t>
+  </si>
+  <si>
+    <t>CT-02: Selecionar sessão e verificar mapa de assentos</t>
+  </si>
+  <si>
+    <t>Sessão ID 1</t>
+  </si>
+  <si>
+    <t>O mapa deve carregar indicando assentos livres e ocupados corretamente.</t>
+  </si>
+  <si>
+    <t>Campo de quantidade de meia-entrada aceita valores negativos</t>
+  </si>
+  <si>
+    <t>RN-03: A quantidade de ingressos meia-entrada não pode ser inferior a zero.</t>
+  </si>
+  <si>
+    <t>CA-03: O input 'qtdMeia' deve ter min=0 e bloquear valores negativos.</t>
+  </si>
+  <si>
+    <t>CT-03: Inserir valor negativo na meia-entrada</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Valor: -1</t>
+  </si>
+  <si>
+    <t>O sistema deve impedir o valor negativo ou tratá-lo como 0, não alterando o total para menos.</t>
+  </si>
+  <si>
+    <t>Validação incorreta de formato de CPF na Etapa 4</t>
+  </si>
+  <si>
+    <t>RN-04: O CPF deve seguir o formato padrão '000.000.000-00'.</t>
+  </si>
+  <si>
+    <t>CA-04: O campo CPF deve validar a estrutura antes de prosseguir.</t>
+  </si>
+  <si>
+    <t>CT-04: Inserir CPF com caracteres inválidos ou incompletos</t>
+  </si>
+  <si>
+    <t>1. Abrir o index.html no navegador.
+2. Inspecionar a seção 'etapa-filme'.
+3. Verificar se os filmes são renderizados.</t>
+  </si>
+  <si>
+    <t>1. Abrir a página.
+2. Clicar em uma sessão de filme.
+3. Observar o mapa de assentos na etapa 2.</t>
+  </si>
+  <si>
+    <t>1. Ir até a Etapa 2.
+2. No campo 'Quantos ingressos são meia-entrada?', digitar '-1'.
+3. Observar o comportamento do sistema.</t>
+  </si>
+  <si>
+    <t>1. Navegar até a Etapa 4 (Seus dados).
+2. Digitar '123' no campo CPF.
+3. Tentar finalizar ou verificar validação.</t>
+  </si>
+  <si>
+    <t>CPF: '123'</t>
+  </si>
+  <si>
+    <t>O sistema deve apontar erro de formato ou preenchimento incompleto.</t>
+  </si>
+  <si>
+    <t>Cupom de desconto válido não aplica o desconto no resumo</t>
+  </si>
+  <si>
+    <t>RN-05: Cupons cadastrados em regras.js devem abater o valor correspondente do total.</t>
+  </si>
+  <si>
+    <t>CA-05: Ao clicar em 'Aplicar', o resumo deve atualizar o valor descontado.</t>
+  </si>
+  <si>
+    <t>CT-05: Aplicar cupom de desconto válido</t>
+  </si>
+  <si>
+    <t>1. Preencher um pedido válido até a Etapa 5.
+2. Digitar um cupom válido (ex: 'CINE10').
+3. Clicar no botão 'Aplicar'.</t>
+  </si>
+  <si>
+    <t>Cupom: 'CINE10'</t>
+  </si>
+  <si>
+    <t>O valor total no resumo deve ser recalculado aplicando o desconto correspondente.</t>
+  </si>
+  <si>
+    <t>Opção de parcelamento não aparece ao selecionar Cartão de Crédito</t>
+  </si>
+  <si>
+    <t>RN-06: O bloco de parcelas deve ser exibido quando a forma de pagamento selecionada for Cartão de Crédito.</t>
+  </si>
+  <si>
+    <t>CA-06: O campo #blocoParcelas deve mudar de hidden para visível ao marcar o rádio de cartão.</t>
+  </si>
+  <si>
+    <t>CT-06: Selecionar forma de pagamento Cartão de Crédito</t>
+  </si>
+  <si>
+    <t>Desconto de 5% do Pix não é aplicado automaticamente no total</t>
+  </si>
+  <si>
+    <t>RN-07: Pagamentos via Pix devem conceder 5% de desconto sobre o valor total do pedido.</t>
+  </si>
+  <si>
+    <t>CA-07: O resumo de valores deve recalcular aplicando o desconto do Pix.</t>
+  </si>
+  <si>
+    <t>CT-07: Validar desconto de Pix no pagamento</t>
+  </si>
+  <si>
+    <t>Erro de layout responsivo na seção de bomboniere em telas menores</t>
+  </si>
+  <si>
+    <t>RN-08: A interface deve se adaptar corretamente a dispositivos móveis e resoluções menores.</t>
+  </si>
+  <si>
+    <t>CA-08: Os itens da bomboniere não devem quebrar o alinhamento da grade em telas de smartphones.</t>
+  </si>
+  <si>
+    <t>CT-08: Testar responsividade da bomboniere em viewport mobile</t>
+  </si>
+  <si>
+    <t>Histórico de compras não persiste após atualizar a página</t>
+  </si>
+  <si>
+    <t>RN-09: As compras confirmadas devem ser armazenadas (ex: localStorage) e exibidas na seção 'Minhas compras'.</t>
+  </si>
+  <si>
+    <t>CA-09: O histórico deve manter os registros mesmo após o refresh do navegador.</t>
+  </si>
+  <si>
+    <t>CT-09: Validar persistência do histórico de compras</t>
+  </si>
+  <si>
+    <t>Botão 'Confirmar compra' permite envio com campos obrigatórios vazios</t>
+  </si>
+  <si>
+    <t>RN-10: O sistema não deve permitir a confirmação da compra se o nome ou e-mail obrigatórios estiverem em branco.</t>
+  </si>
+  <si>
+    <t>CA-10: Exibir mensagem de erro no elemento #mensagens caso dados obrigatórios faltem.</t>
+  </si>
+  <si>
+    <t>CT-10: Tentar confirmar compra sem preencher dados do cliente</t>
+  </si>
+  <si>
+    <t>Tempo de carregamento da página principal em conexão simulada Slow 4G.</t>
+  </si>
+  <si>
+    <t>1. Abrir o Google Chrome DevTools. 2. Acessar a aba Network. 3. Configurar o throttling para 'Slow 4G' e marcar 'Disable cache'. 4. Acessar a página e registrar o tempo de load completo.</t>
+  </si>
+  <si>
+    <t>A página deve ficar utilizável em até 3 segundos em conexão 'Slow 4G'.</t>
+  </si>
+  <si>
+    <t>Nenhum</t>
+  </si>
+  <si>
+    <t>Tamanho dos arquivos de imagem utilizados na aplicação.</t>
+  </si>
+  <si>
+    <t>1. Inspecionar os recursos de imagem na aba Network do DevTools. 2. Verificar o tamanho (payload) de cada imagem carregada.</t>
+  </si>
+  <si>
+    <t>Maior imagem com 180 KB</t>
+  </si>
+  <si>
+    <t>Nenhuma imagem pode passar de 300 KB.</t>
+  </si>
+  <si>
+    <t>Capacidade do sistema de sanitizar entradas e evitar execução de scripts/HTML injetados.</t>
+  </si>
+  <si>
+    <t>1. Inserir tags HTML maliciosas ou de formatação (ex: &lt;b&gt;Ana&lt;/b&gt;) no campo de nome completo. 2. Concluir a compra e inspecionar a tela de confirmação.</t>
+  </si>
+  <si>
+    <t>Exibido como texto literal (sem execução)</t>
+  </si>
+  <si>
+    <t>Tudo o que o cliente digita é exibido como texto. Código HTML ou JavaScript digitado nunca é executado.</t>
+  </si>
+  <si>
+    <t>Navegabilidade completa e funcionalidade do fluxo de compra sem o uso do mouse.</t>
+  </si>
+  <si>
+    <t>1. Desconectar o mouse. 2. Utilizar exclusivamente as teclas Tab, Shift+Tab, setas direcionais, Enter e Espaço para percorrer todo o fluxo de escolha de filme, assentos, bomboniere e pagamento.</t>
+  </si>
+  <si>
+    <t>Fluxo concluído com 100% de sucesso via teclado</t>
+  </si>
+  <si>
+    <t>A compra inteira pode ser feita só com o teclado (Tab, Shift+Tab, setas, Enter e Espaço).</t>
+  </si>
+  <si>
+    <t>Padronização da formatação de valores monetários na interface.</t>
+  </si>
+  <si>
+    <t>1. Adicionar ingressos, itens de bomboniere e aplicar cupons. 2. Inspecionar visualmente todos os campos de exibição monetária no resumo do pedido.</t>
+  </si>
+  <si>
+    <t>100% dos campos no formato R$ XX,XX</t>
+  </si>
+  <si>
+    <t>Todos os valores em dinheiro aparecem no formato brasileiro, com R$, vírgula e duas casas decimais.</t>
+  </si>
+  <si>
+    <t>if (hora &lt;= 17) { return 24; }</t>
+  </si>
+  <si>
+    <t>Caminho verdadeiro (hora &lt;= 17)</t>
+  </si>
+  <si>
+    <t>sessao = { hora: '14:00' }</t>
+  </si>
+  <si>
+    <t>Retornar 24 (preço de matinê)</t>
+  </si>
+  <si>
+    <t>if (hora &lt;= 17) { return 24; } else { return 32; }</t>
+  </si>
+  <si>
+    <t>Caminho falso (hora &gt; 17)</t>
+  </si>
+  <si>
+    <t>sessao = { hora: '20:30' }</t>
+  </si>
+  <si>
+    <t>Retornar 32 (sessão a partir das 17:00)</t>
+  </si>
+  <si>
+    <t>if (sessao.tipo === 'pre-estreia') { meias = 0; }</t>
+  </si>
+  <si>
+    <t>Caminho verdadeiro (sessão do tipo pré-estreia)</t>
+  </si>
+  <si>
+    <t>sessao = { tipo: 'pre-estreia', formato: '2D', hora: '22:00' }, quantidade = 1, quantidadeMeia = 1, precoBase = 32</t>
+  </si>
+  <si>
+    <t>Zerar quantidade de meias, cobrando valor de inteira (R$ 32,00)</t>
+  </si>
+  <si>
+    <t>if (subtotalBomboniere &gt;= 20) dentro do bloco CUPOM PIPOCA5</t>
+  </si>
+  <si>
+    <t>Caminho falso (subtotal da bomboniere abaixo do limite interno da função)</t>
+  </si>
+  <si>
+    <t>codigo = 'PIPOCA5', subtotalIngressos = 32, subtotalBomboniere = 15</t>
+  </si>
+  <si>
+    <t>Retornar valido: false, valor: 0 e mensagem de restrição de bomboniere</t>
+  </si>
+  <si>
+    <t>if (quantidadeIngressos &lt;= 0) { return 0; }</t>
+  </si>
+  <si>
+    <t>Caminho verdadeiro (quantidade de ingressos menor ou igual a zero)</t>
+  </si>
+  <si>
+    <t>quantidadeIngressos = 0, quantidadeItens = 2</t>
+  </si>
+  <si>
+    <t>Retornar taxa igual a 0</t>
+  </si>
+  <si>
+    <t>Verifica se o preço base cobrado para uma sessão de matinê (14:00) é de R$ 24,00.</t>
+  </si>
+  <si>
+    <t>testar('AT01', 'Sessão 14:00 custa R$ 24,00', precoBaseSessao(sessao('orb-1400')), 24);</t>
+  </si>
+  <si>
+    <t>PASSOU</t>
+  </si>
+  <si>
+    <t>Verifica se o preço base cobrado para uma sessão após as 17:00 (21:00) é de R$ 32,00.</t>
+  </si>
+  <si>
+    <t>testar('AT02', 'Sessão 21:00 custa R$ 32,00', precoBaseSessao(sessao('far-2100')), 32);</t>
+  </si>
+  <si>
+    <t>Verifica o cálculo de ingressos considerando o adicional 3D (R$ 6,00 por ingresso às 20:30).</t>
+  </si>
+  <si>
+    <t>testar('AT03', '2 inteiras em sessão 3D 20:30 custam R$ 76,00', calcularIngressos(sessao('orb-2030'), 2, 0, 32), 76);</t>
+  </si>
+  <si>
+    <t>Verifica se sessões de pré-estreia desconsideram meia-entrada e cobram inteira.</t>
+  </si>
+  <si>
+    <t>testar('AT04', 'Pré-estreia não aceita meia e cobra inteira', calcularIngressos(sessao('vid-2200'), 1, 1, 32), 38);</t>
+  </si>
+  <si>
+    <t>FALHOU</t>
+  </si>
+  <si>
+    <t>BUG-01 (Função aplica desconto de meia em pré-estreia)</t>
+  </si>
+  <si>
+    <t>Verifica o cálculo da taxa de conveniência (R$ 2,50 por ingresso) sem incidir na bomboniere.</t>
+  </si>
+  <si>
+    <t>testar('AT05', '2 ingressos e 2 itens geram R$ 10,00 de taxa', calcularTaxa(2, 2), 10);</t>
+  </si>
+  <si>
+    <t>Verifica a recusa do cupom PIPOCA5 quando a bomboniere está abaixo de R$ 25,00.</t>
+  </si>
+  <si>
+    <t>testar('AT06', 'PIPOCA5 recusado abaixo de R$ 25,00', calcularDescontoCupom('PIPOCA5', 32, 14).valido, false);</t>
+  </si>
+  <si>
+    <t>BUG-02 (Validação de bomboniere no cupom verifica R$ 20,00 em vez de R$ 25,00)</t>
+  </si>
+  <si>
+    <t>Verifica a validação de CPF inválido contendo menos de 10 dígitos.</t>
+  </si>
+  <si>
+    <t>testar('AT07', 'CPF com menos de 10 dígitos é rejeitado', validarCPF('123456789'), false);</t>
+  </si>
+  <si>
+    <t>O valor do ingresso exibido R$24,00</t>
+  </si>
+  <si>
+    <t>O valor do ingresso exibido R$32,00</t>
+  </si>
+  <si>
+    <t>O Valor do ingresso exibido R$ 70,00</t>
+  </si>
+  <si>
+    <t>O valor exibido : R$25,20</t>
+  </si>
+  <si>
+    <t>Valor exibido: R$ 19,20</t>
+  </si>
+  <si>
+    <t>O setimo acento foi selecionado</t>
+  </si>
+  <si>
+    <t>O acento e desmacado e valor e resetado</t>
+  </si>
+  <si>
+    <t>O valor não saiu do valor 10</t>
+  </si>
+  <si>
+    <t>Foi incluido o valor de conveniencia sobre os items da bomboniere</t>
+  </si>
+  <si>
+    <t>O valor do cupom foi aplicado corretamente.</t>
+  </si>
+  <si>
+    <t>A Aplicação de Cupom foi recusada</t>
+  </si>
+  <si>
+    <t>O desconto do pix não foi removido</t>
+  </si>
+  <si>
+    <t>O numero de parcelas esta com 3 parcelas</t>
+  </si>
+  <si>
+    <t>O sistema mostrou a message quando digitou nome com 2 letras, e procegui quando digitou com 3 letras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O sistema se recusou a continuar </t>
+  </si>
+  <si>
+    <t>Todos os valores foram resetados</t>
+  </si>
+  <si>
+    <t>O nome foi apresentado em negrito</t>
+  </si>
+  <si>
+    <t>Não consegui escolher os acentos</t>
+  </si>
+  <si>
+    <t>O valores esta corretos e exibido em real</t>
+  </si>
+  <si>
+    <t>Todos os filmes estão renderizados</t>
+  </si>
+  <si>
+    <t>Todos estão carregado corretamente de acordo com o filme</t>
+  </si>
+  <si>
+    <t>O sistema não fz nada</t>
+  </si>
+  <si>
+    <t>Uma messagem aparece dizendo que o cpf era invalido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O disconto foi aplicado </t>
+  </si>
+  <si>
+    <t>32,25 segundos</t>
+  </si>
+  <si>
+    <t>{valido: false, valor: 0, mensagem: 'O cupom PIPOCA5 exige no mínimo R$ 25,00 em bomboniere.'}</t>
+  </si>
+  <si>
+    <t>Valor retornado 0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -2073,8 +2492,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1B2440"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2105,8 +2539,14 @@
         <bgColor rgb="FFDCE3F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2142,73 +2582,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1A4B54C5-1465-4A49-A369-0CDE623FDEF0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2279,6 +2746,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFF7DC"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2698,18 +3168,18 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2717,25 +3187,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>158</v>
@@ -2743,125 +3213,237 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>332</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>333</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>94</v>
       </c>
       <c r="E5" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>335</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
       <c r="I5" s="14"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="F6" s="8">
+        <v>24</v>
+      </c>
+      <c r="G6" s="8">
+        <v>24</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="F7" s="8">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="F8" s="8">
+        <v>76</v>
+      </c>
+      <c r="G8" s="8">
+        <v>76</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="F9" s="8">
+        <v>38</v>
+      </c>
+      <c r="G9" s="8">
+        <v>32</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="F10" s="8">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8">
+        <v>10</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2874,7 +3456,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -2887,7 +3469,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2900,7 +3482,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2913,7 +3495,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2926,7 +3508,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2939,7 +3521,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2952,7 +3534,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2965,7 +3547,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2978,7 +3560,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2991,7 +3573,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -3004,7 +3586,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3017,7 +3599,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -3086,12 +3668,12 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3099,42 +3681,42 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="10" t="s">
         <v>366</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3150,7 +3732,7 @@
     </row>
     <row r="6" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3166,7 +3748,7 @@
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3222,50 +3804,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5" s="18">
         <f>COUNTA('5_Casos_de_Teste'!G6:G45)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B6" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Passou")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Falhou")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B8" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Bloqueado")</f>
@@ -3274,7 +3856,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B9" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!M6:M45,"Não executado")</f>
@@ -3283,16 +3865,16 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B10" s="19">
         <f>IFERROR(B6/(B6+B7+B8),0)</f>
-        <v>0</v>
+        <v>0.52631578947368418</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B11" s="18">
         <f>COUNTIF('5_Casos_de_Teste'!D6:D45,"Valor limite")</f>
@@ -3301,16 +3883,16 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B12" s="18">
         <f>COUNTA('6_Bugs'!B6:B35)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B13" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Crítica")</f>
@@ -3319,16 +3901,16 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B14" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Alta")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B15" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Média")</f>
@@ -3337,7 +3919,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B16" s="18">
         <f>COUNTIF('6_Bugs'!G6:G35,"Baixa")</f>
@@ -3346,7 +3928,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B17" s="18">
         <f>COUNTIF('6_Bugs'!N6:N35,"Corrigido*")</f>
@@ -3355,129 +3937,129 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B18" s="18">
         <f>COUNTA('7_Nao_Funcionais'!H6:H20)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B19" s="18">
         <f>COUNTIF('7_Nao_Funcionais'!H6:H20,"Falhou")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B20" s="18">
         <f>COUNTA('8_Caixa_Branca'!C6:C25)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B21" s="18">
         <f>COUNTA('9_Automacao'!E6:E25)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B22" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Passou")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B23" s="18">
         <f>COUNTIF('9_Automacao'!H6:H25,"Falhou")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="9" t="s">
         <v>394</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="9" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
+        <v>395</v>
+      </c>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
     </row>
     <row r="28" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
+        <v>396</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
     </row>
     <row r="29" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
+        <v>397</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="9" t="s">
         <v>399</v>
-      </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="9" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="9" t="s">
         <v>401</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="9" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
+        <v>402</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
     </row>
     <row r="33" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
+        <v>403</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3525,13 +4107,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>405</v>
+      <c r="A1" s="32" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3542,24 +4124,24 @@
         <v>219</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>410</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -3570,7 +4152,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3581,7 +4163,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3592,7 +4174,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3603,7 +4185,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3614,7 +4196,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -3625,7 +4207,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3636,7 +4218,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -3647,7 +4229,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3658,7 +4240,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3698,13 +4280,13 @@
         <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>157</v>
@@ -3716,36 +4298,36 @@
         <v>215</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>84</v>
       </c>
       <c r="L1" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>431</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>162</v>
@@ -3754,7 +4336,7 @@
         <v>134</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>170</v>
@@ -3769,45 +4351,45 @@
         <v>229</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>441</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>443</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>145</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>446</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>41</v>
@@ -3816,39 +4398,39 @@
         <v>43</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>451</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>452</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>455</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>135</v>
@@ -3857,7 +4439,7 @@
         <v>163</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>43</v>
@@ -3866,30 +4448,30 @@
         <v>45</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>230</v>
       </c>
       <c r="O4" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>463</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>136</v>
@@ -3898,98 +4480,98 @@
         <v>145</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>137</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M6" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>473</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>137</v>
       </c>
       <c r="M7" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>138</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>481</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>139</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>140</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -4000,23 +4582,23 @@
         <v>141</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>142</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>143</v>
@@ -4032,45 +4614,45 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>487</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4103,7 +4685,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -4111,7 +4693,7 @@
         <v>50</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -4119,7 +4701,7 @@
         <v>51</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>52</v>
@@ -4141,7 +4723,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>56</v>
@@ -4152,7 +4734,7 @@
         <v>57</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>58</v>
@@ -4227,10 +4809,10 @@
         <v>69</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4241,7 +4823,7 @@
         <v>71</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D6" s="8"/>
     </row>
@@ -4253,7 +4835,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D7" s="8"/>
     </row>
@@ -4265,7 +4847,7 @@
         <v>75</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D8" s="8"/>
     </row>
@@ -4277,7 +4859,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D9" s="8"/>
     </row>
@@ -4289,7 +4871,7 @@
         <v>79</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D10" s="8"/>
     </row>
@@ -4301,7 +4883,7 @@
         <v>81</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D11" s="8"/>
     </row>
@@ -4313,7 +4895,7 @@
         <v>83</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D12" s="8"/>
     </row>
@@ -4322,7 +4904,7 @@
         <v>84</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4330,7 +4912,7 @@
         <v>85</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D16" s="24"/>
     </row>
@@ -4434,19 +5016,19 @@
         <v>99</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="E6" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="F6" s="23" t="s">
         <v>515</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -4457,16 +5039,16 @@
         <v>94</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E7" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>517</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -4611,7 +5193,7 @@
         <v>111</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4619,7 +5201,7 @@
         <v>112</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>113</v>
@@ -4630,7 +5212,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4638,7 +5220,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>116</v>
@@ -4649,7 +5231,7 @@
         <v>117</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -4657,7 +5239,7 @@
         <v>118</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>119</v>
@@ -4668,7 +5250,7 @@
         <v>120</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>121</v>
@@ -4679,7 +5261,7 @@
         <v>122</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>123</v>
@@ -4690,7 +5272,7 @@
         <v>124</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>125</v>
@@ -4701,7 +5283,7 @@
         <v>126</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>127</v>
@@ -4737,10 +5319,10 @@
         <v>134</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -4748,10 +5330,10 @@
         <v>135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -4759,7 +5341,7 @@
         <v>136</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C21" s="8"/>
     </row>
@@ -4768,10 +5350,10 @@
         <v>137</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -4779,7 +5361,7 @@
         <v>138</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C23" s="8"/>
     </row>
@@ -4788,10 +5370,10 @@
         <v>139</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -4799,10 +5381,10 @@
         <v>140</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -4810,7 +5392,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C26" s="8"/>
     </row>
@@ -4819,7 +5401,7 @@
         <v>142</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C27" s="8"/>
     </row>
@@ -4828,7 +5410,7 @@
         <v>143</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C28" s="8"/>
     </row>
@@ -4837,10 +5419,10 @@
         <v>144</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -4848,10 +5430,10 @@
         <v>145</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
@@ -5013,10 +5595,10 @@
         <v>171</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>162</v>
@@ -5028,22 +5610,26 @@
         <v>163</v>
       </c>
       <c r="G6" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>528</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="I6" s="23" t="s">
         <v>529</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="J6" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="23" t="s">
         <v>531</v>
       </c>
-      <c r="K6" s="23" t="s">
-        <v>532</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="L6" s="23" t="s">
+        <v>749</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
@@ -5052,13 +5638,13 @@
         <v>172</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>134</v>
@@ -5067,22 +5653,26 @@
         <v>163</v>
       </c>
       <c r="G7" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>534</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="I7" s="23" t="s">
         <v>535</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="23" t="s">
         <v>537</v>
       </c>
-      <c r="K7" s="23" t="s">
-        <v>538</v>
-      </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
+      <c r="L7" s="23" t="s">
+        <v>750</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
@@ -5091,10 +5681,10 @@
         <v>173</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>162</v>
@@ -5106,22 +5696,26 @@
         <v>163</v>
       </c>
       <c r="G8" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="I8" s="23" t="s">
         <v>540</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="I8" s="23" t="s">
+      <c r="J8" s="23" t="s">
         <v>541</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="K8" s="23" t="s">
         <v>542</v>
       </c>
-      <c r="K8" s="23" t="s">
-        <v>543</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
+      <c r="L8" s="23" t="s">
+        <v>751</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
@@ -5130,10 +5724,10 @@
         <v>174</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>162</v>
@@ -5145,22 +5739,26 @@
         <v>163</v>
       </c>
       <c r="G9" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="I9" s="23" t="s">
         <v>545</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="I9" s="23" t="s">
+      <c r="J9" s="23" t="s">
         <v>546</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>547</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>548</v>
-      </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="L9" s="23" t="s">
+        <v>752</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
@@ -5169,10 +5767,10 @@
         <v>175</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>162</v>
@@ -5184,22 +5782,26 @@
         <v>163</v>
       </c>
       <c r="G10" s="23" t="s">
+        <v>548</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>549</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>535</v>
-      </c>
-      <c r="I10" s="23" t="s">
+      <c r="J10" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="23" t="s">
         <v>551</v>
       </c>
-      <c r="K10" s="23" t="s">
-        <v>552</v>
-      </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="L10" s="23" t="s">
+        <v>753</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
@@ -5208,13 +5810,13 @@
         <v>176</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>134</v>
@@ -5223,22 +5825,26 @@
         <v>163</v>
       </c>
       <c r="G11" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="H11" s="23" t="s">
         <v>553</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="I11" s="23" t="s">
         <v>554</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="J11" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="23" t="s">
         <v>556</v>
       </c>
-      <c r="K11" s="23" t="s">
-        <v>557</v>
-      </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="L11" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
@@ -5247,10 +5853,10 @@
         <v>177</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>162</v>
@@ -5262,22 +5868,26 @@
         <v>163</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="L12" s="23" t="s">
+        <v>755</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>170</v>
+      </c>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
@@ -5286,13 +5896,13 @@
         <v>178</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>134</v>
@@ -5301,22 +5911,26 @@
         <v>163</v>
       </c>
       <c r="G13" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="22" t="s">
         <v>567</v>
       </c>
-      <c r="K13" s="22" t="s">
-        <v>568</v>
-      </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
+      <c r="L13" s="23" t="s">
+        <v>756</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
@@ -5325,10 +5939,10 @@
         <v>179</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>162</v>
@@ -5340,22 +5954,26 @@
         <v>163</v>
       </c>
       <c r="G14" s="23" t="s">
+        <v>569</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="23" t="s">
         <v>571</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="J14" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="L14" s="22"/>
-      <c r="M14" s="8"/>
+      <c r="L14" s="22" t="s">
+        <v>757</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
     </row>
@@ -5364,13 +5982,13 @@
         <v>180</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>575</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>576</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>134</v>
@@ -5379,22 +5997,26 @@
         <v>163</v>
       </c>
       <c r="G15" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="J15" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
+      <c r="L15" s="22" t="s">
+        <v>758</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
     </row>
@@ -5406,10 +6028,10 @@
         <v>222</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>134</v>
@@ -5418,34 +6040,38 @@
         <v>163</v>
       </c>
       <c r="G16" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="L16" s="22" t="s">
+        <v>759</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" s="25" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="27" t="s">
         <v>182</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>162</v>
@@ -5457,22 +6083,26 @@
         <v>163</v>
       </c>
       <c r="G17" s="23" t="s">
+        <v>588</v>
+      </c>
+      <c r="H17" s="23" t="s">
         <v>589</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="I17" s="23" t="s">
         <v>590</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="J17" s="23" t="s">
         <v>591</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="K17" s="23" t="s">
         <v>592</v>
       </c>
-      <c r="K17" s="23" t="s">
-        <v>593</v>
-      </c>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
+      <c r="L17" s="23" t="s">
+        <v>760</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>445</v>
+      </c>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
     </row>
@@ -5481,13 +6111,13 @@
         <v>183</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>134</v>
@@ -5496,22 +6126,26 @@
         <v>163</v>
       </c>
       <c r="G18" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="J18" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="L18" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
     </row>
@@ -5523,10 +6157,10 @@
         <v>94</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>134</v>
@@ -5535,22 +6169,26 @@
         <v>163</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
+      <c r="L19" s="23" t="s">
+        <v>762</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
     </row>
@@ -5574,22 +6212,26 @@
         <v>163</v>
       </c>
       <c r="G20" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="J20" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
+      <c r="L20" s="22" t="s">
+        <v>763</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
     </row>
@@ -5598,10 +6240,10 @@
         <v>186</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>137</v>
@@ -5613,22 +6255,26 @@
         <v>163</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
+      <c r="L21" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
     </row>
@@ -5637,10 +6283,10 @@
         <v>187</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>142</v>
@@ -5652,22 +6298,26 @@
         <v>163</v>
       </c>
       <c r="G22" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="23" t="s">
         <v>619</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
+      <c r="L22" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
     </row>
@@ -5676,10 +6326,10 @@
         <v>188</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>137</v>
@@ -5691,22 +6341,26 @@
         <v>163</v>
       </c>
       <c r="G23" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
+      <c r="L23" s="23" t="s">
+        <v>766</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
@@ -5715,10 +6369,10 @@
         <v>189</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>629</v>
+        <v>492</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>628</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>162</v>
@@ -5730,59 +6384,43 @@
         <v>163</v>
       </c>
       <c r="G24" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
+      <c r="L24" s="23" t="s">
+        <v>767</v>
+      </c>
+      <c r="M24" s="22" t="s">
+        <v>170</v>
+      </c>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" ht="66" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>641</v>
-      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -6232,9 +6870,9 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
@@ -6349,218 +6987,366 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>637</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>658</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>639</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>640</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>768</v>
+      </c>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+    </row>
+    <row r="7" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B7" s="29" t="s">
+        <v>641</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>642</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>643</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>644</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>646</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>769</v>
+      </c>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+    </row>
+    <row r="8" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
+        <v>647</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>648</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>649</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>650</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>660</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>770</v>
+      </c>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+    </row>
+    <row r="9" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
+      <c r="B9" s="29" t="s">
+        <v>654</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>655</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>656</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>662</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>771</v>
+      </c>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+    </row>
+    <row r="11" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="29" t="s">
+        <v>664</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>666</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>667</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>668</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>669</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>670</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>772</v>
+      </c>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+    </row>
+    <row r="12" spans="1:15" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="29" t="s">
+        <v>671</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>672</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>673</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>674</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="29" t="s">
+        <v>675</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>676</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>677</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>678</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+    </row>
+    <row r="14" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="B14" s="29" t="s">
+        <v>679</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>680</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>681</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>682</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+    </row>
+    <row r="15" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="29" t="s">
+        <v>683</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>684</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>685</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>686</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
+      <c r="B16" s="29" t="s">
+        <v>687</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>688</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>689</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>690</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -6579,7 +7365,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6598,7 +7384,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -6617,7 +7403,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -6636,7 +7422,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -6655,7 +7441,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -6674,7 +7460,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -6693,7 +7479,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6705,14 +7491,14 @@
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="23"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -6731,7 +7517,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6750,7 +7536,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -6769,7 +7555,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -6788,7 +7574,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -6807,7 +7593,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -6826,7 +7612,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -6845,7 +7631,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -6864,7 +7650,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -6883,7 +7669,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -6902,7 +7688,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -6921,7 +7707,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
@@ -7004,12 +7790,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7023,16 +7809,16 @@
         <v>88</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>157</v>
@@ -7046,121 +7832,181 @@
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>139</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>272</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>170</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>274</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>773</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="I7" s="22"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>276</v>
-      </c>
       <c r="B8" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>445</v>
+      </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+        <v>144</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>445</v>
+      </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+        <v>487</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>694</v>
+      </c>
       <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>143</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -7172,11 +8018,9 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>144</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -7188,7 +8032,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -7202,7 +8046,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -7216,7 +8060,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -7230,7 +8074,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -7244,7 +8088,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -7258,7 +8102,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -7272,7 +8116,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -7286,11 +8130,11 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="D20" s="22"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -7356,12 +8200,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7369,19 +8213,19 @@
         <v>64</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>295</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>156</v>
@@ -7398,25 +8242,25 @@
     </row>
     <row r="5" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>302</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>170</v>
@@ -7426,79 +8270,159 @@
       </c>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="G6" s="8">
+        <v>24</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="G7" s="8">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="G8" s="31">
+        <v>32</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>775</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>479</v>
+      </c>
       <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -7512,7 +8436,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -7526,7 +8450,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -7540,21 +8464,21 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -7568,7 +8492,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -7582,7 +8506,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -7596,11 +8520,11 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="D18" s="22"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -7610,7 +8534,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -7624,7 +8548,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -7638,7 +8562,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -7652,7 +8576,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -7666,7 +8590,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -7680,7 +8604,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -7694,7 +8618,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
